--- a/cropvideo/marathi.xlsx
+++ b/cropvideo/marathi.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dhaneshkumarkapadia/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dhaneshkumarkapadia/Desktop/swinTransformer/cropvideo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58ED2906-3B01-4647-8194-AD619C4D755C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EA2B0A7-8C44-B843-BE8C-68CBC0420B53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="140" yWindow="600" windowWidth="26740" windowHeight="15200" xr2:uid="{F583F2BC-D1B1-3A48-88E7-21C7FADE06E4}"/>
+    <workbookView xWindow="140" yWindow="600" windowWidth="26740" windowHeight="15200" activeTab="2" xr2:uid="{F583F2BC-D1B1-3A48-88E7-21C7FADE06E4}"/>
   </bookViews>
   <sheets>
     <sheet name="hemant" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="209">
   <si>
     <t xml:space="preserve">अ   </t>
   </si>
@@ -662,6 +662,54 @@
   <si>
     <t>paragraph1</t>
   </si>
+  <si>
+    <t>00:01:10:510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">बोट </t>
+  </si>
+  <si>
+    <t>कांदा</t>
+  </si>
+  <si>
+    <t>दगड</t>
+  </si>
+  <si>
+    <t>थ्ड्डी</t>
+  </si>
+  <si>
+    <t>नऊ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">वेड </t>
+  </si>
+  <si>
+    <t xml:space="preserve">एकदा </t>
+  </si>
+  <si>
+    <t>कापड</t>
+  </si>
+  <si>
+    <t>स्वातंत्र्य</t>
+  </si>
+  <si>
+    <t>दौड</t>
+  </si>
+  <si>
+    <t>पुरवणी</t>
+  </si>
+  <si>
+    <t>शून्य</t>
+  </si>
+  <si>
+    <t>चहा</t>
+  </si>
+  <si>
+    <t>जडी</t>
+  </si>
+  <si>
+    <t>S5</t>
+  </si>
 </sst>
 </file>
 
@@ -670,7 +718,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="hh:mm:ss.000"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -772,6 +820,26 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -793,7 +861,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -825,6 +893,10 @@
       <alignment horizontal="left" vertical="center" indent="6"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2892,7 +2964,7 @@
         <v>1.2396064814814815E-3</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="35" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:3" ht="33" x14ac:dyDescent="0.35">
       <c r="A76" s="11" t="s">
         <v>147</v>
       </c>
@@ -3358,550 +3430,1241 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE244C9E-E386-994D-85D3-5E78C59DD058}">
-  <dimension ref="A1:A116"/>
+  <dimension ref="A1:G129"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="57.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.5" style="9" customWidth="1"/>
+    <col min="3" max="3" width="20.1640625" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="31" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="31" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="B2" s="9">
+        <v>9.6886574074074079E-5</v>
+      </c>
+      <c r="C2" s="9">
+        <v>1.0678240740740742E-4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="B3" s="9">
+        <v>1.1141203703703704E-4</v>
+      </c>
+      <c r="C3" s="9">
+        <v>1.2376157407407407E-4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="B5" s="9">
+        <v>1.4465277777777778E-4</v>
+      </c>
+      <c r="C5" s="9">
+        <v>1.5890046296296296E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+      <c r="B6" s="9">
+        <v>1.6380787037037037E-4</v>
+      </c>
+      <c r="C6" s="9">
+        <v>1.7270833333333333E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="B7" s="9">
+        <v>1.7629629629629628E-4</v>
+      </c>
+      <c r="C7" s="9">
+        <v>1.863425925925926E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+      <c r="B8" s="9">
+        <v>1.8928240740740741E-4</v>
+      </c>
+      <c r="C8" s="9">
+        <v>1.9906250000000002E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="B9" s="9">
+        <v>2.0140046296296296E-4</v>
+      </c>
+      <c r="C9" s="9">
+        <v>2.1181712962962962E-4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="B10" s="9">
+        <v>2.1734953703703703E-4</v>
+      </c>
+      <c r="C10" s="9">
+        <v>2.280671296296296E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+      <c r="B11" s="9">
+        <v>2.3331018518518519E-4</v>
+      </c>
+      <c r="C11" s="9">
+        <v>2.4476851851851851E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+      <c r="B12" s="9">
+        <v>2.4795138888888886E-4</v>
+      </c>
+      <c r="C12" s="9">
+        <v>2.5835648148148148E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+      <c r="B13" s="9">
+        <v>2.6113425925925929E-4</v>
+      </c>
+      <c r="C13" s="9">
+        <v>2.7217592592592593E-4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+      <c r="B14" s="9">
+        <v>2.7472222222222221E-4</v>
+      </c>
+      <c r="C14" s="9">
+        <v>2.8474537037037037E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+      <c r="B15" s="9">
+        <v>2.8684027777777779E-4</v>
+      </c>
+      <c r="C15" s="9">
+        <v>3.0094907407407409E-4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+      <c r="B16" s="9">
+        <v>3.0579861111111113E-4</v>
+      </c>
+      <c r="C16" s="9">
+        <v>3.1416666666666664E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" ht="31" x14ac:dyDescent="0.2">
-      <c r="A18" s="2" t="s">
+      <c r="B17" s="9">
+        <v>3.1593750000000003E-4</v>
+      </c>
+      <c r="C17" s="9">
+        <v>3.2493055555555557E-4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="31" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
+      <c r="B19" s="9">
+        <v>3.3023148148148148E-4</v>
+      </c>
+      <c r="C19" s="9">
+        <v>3.3936342592592595E-4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+      <c r="B20" s="9">
+        <v>3.4015046296296294E-4</v>
+      </c>
+      <c r="C20" s="9">
+        <v>3.4935185185185188E-4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
+      <c r="B21" s="9">
+        <v>3.5131944444444441E-4</v>
+      </c>
+      <c r="C21" s="9">
+        <v>3.6116898148148146E-4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+      <c r="B22" s="9">
+        <v>3.623611111111111E-4</v>
+      </c>
+      <c r="C22" s="9">
+        <v>3.7266203703703702E-4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" ht="31" x14ac:dyDescent="0.2">
-      <c r="A23" s="2" t="s">
+      <c r="B23" s="9">
+        <v>3.7447916666666662E-4</v>
+      </c>
+      <c r="C23" s="9">
+        <v>3.8442129629629628E-4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="31" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+      <c r="B24" s="9">
+        <v>3.8715277777777782E-4</v>
+      </c>
+      <c r="C24" s="9">
+        <v>3.9642361111111107E-4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+      <c r="B25" s="9">
+        <v>3.983912037037037E-4</v>
+      </c>
+      <c r="C25" s="9">
+        <v>4.0821759259259262E-4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+      <c r="B26" s="9">
+        <v>4.1078703703703698E-4</v>
+      </c>
+      <c r="C26" s="9">
+        <v>4.1875000000000001E-4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
+      <c r="B27" s="9">
+        <v>4.3930555555555558E-4</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:1" ht="31" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
+    <row r="29" spans="1:3" ht="31" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
+      <c r="B29" s="9">
+        <v>4.5622685185185187E-4</v>
+      </c>
+      <c r="C29" s="9">
+        <v>4.6372685185185189E-4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
+      <c r="B30" s="9">
+        <v>4.6643518518518513E-4</v>
+      </c>
+      <c r="C30" s="9">
+        <v>4.7486111111111112E-4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
+      <c r="B31" s="9">
+        <v>4.7619212962962963E-4</v>
+      </c>
+      <c r="C31" s="9">
+        <v>4.8493055555555561E-4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
+      <c r="B32" s="9">
+        <v>4.8681712962962963E-4</v>
+      </c>
+      <c r="C32" s="9">
+        <v>4.9417824074074078E-4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" ht="31" x14ac:dyDescent="0.2">
-      <c r="A33" s="2" t="s">
+      <c r="B33" s="9">
+        <v>4.955787037037037E-4</v>
+      </c>
+      <c r="C33" s="9">
+        <v>5.0260416666666661E-4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="31" x14ac:dyDescent="0.2">
+      <c r="A34" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
+      <c r="B34" s="9">
+        <v>5.0758101851851843E-4</v>
+      </c>
+      <c r="C34" s="9">
+        <v>5.1568287037037034E-4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
+      <c r="B35" s="9">
+        <v>5.173032407407407E-4</v>
+      </c>
+      <c r="C35" s="9">
+        <v>5.2527777777777783E-4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
+      <c r="B36" s="9">
+        <v>5.261921296296296E-4</v>
+      </c>
+      <c r="C36" s="9">
+        <v>5.345023148148148E-4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
+      <c r="B37" s="9">
+        <v>5.3643518518518515E-4</v>
+      </c>
+      <c r="C37" s="9">
+        <v>5.4347222222222221E-4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" ht="31" x14ac:dyDescent="0.2">
-      <c r="A38" s="2" t="s">
+      <c r="B38" s="9">
+        <v>5.4430555555555558E-4</v>
+      </c>
+      <c r="C38" s="9">
+        <v>5.5127314814814817E-4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="31" x14ac:dyDescent="0.2">
+      <c r="A39" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
+      <c r="B39" s="9">
+        <v>5.593287037037037E-4</v>
+      </c>
+      <c r="C39" s="9">
+        <v>5.6770833333333326E-4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
+      <c r="B40" s="9">
+        <v>5.6770833333333326E-4</v>
+      </c>
+      <c r="C40" s="9">
+        <v>5.7641203703703706E-4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
+      <c r="B41" s="9">
+        <v>5.7659722222222216E-4</v>
+      </c>
+      <c r="C41" s="9">
+        <v>5.8425925925925919E-4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
+      <c r="B42" s="9">
+        <v>5.8414351851851845E-4</v>
+      </c>
+      <c r="C42" s="9">
+        <v>5.8937499999999995E-4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
+      <c r="B43" s="9">
+        <v>5.8937499999999995E-4</v>
+      </c>
+      <c r="C43" s="9">
+        <v>5.944907407407407E-4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
+      <c r="B44" s="9">
+        <v>5.9924768518518519E-4</v>
+      </c>
+      <c r="C44" s="9">
+        <v>6.0488425925925922E-4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
+      <c r="B47" s="9">
+        <v>6.1914351851851855E-4</v>
+      </c>
+      <c r="C47" s="9">
+        <v>6.2335648148148146E-4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
+      <c r="B48" s="9">
+        <v>6.2540509259259255E-4</v>
+      </c>
+      <c r="C48" s="9">
+        <v>6.3096064814814818E-4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
+      <c r="B49" s="9">
+        <v>6.3105324074074073E-4</v>
+      </c>
+      <c r="C49" s="9">
+        <v>6.3577546296296299E-4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
+      <c r="B51" s="9">
+        <v>6.3577546296296299E-4</v>
+      </c>
+      <c r="C51" s="9">
+        <v>6.3949074074074082E-4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A53" s="4" t="s">
+      <c r="B52" s="9">
+        <v>6.4016203703703707E-4</v>
+      </c>
+      <c r="C52" s="9">
+        <v>6.4458333333333338E-4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="62" spans="1:1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A62" s="5" t="s">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>206</v>
+      </c>
+      <c r="B62" s="9">
+        <v>1.6096643518518517E-3</v>
+      </c>
+      <c r="C62" s="9">
+        <v>1.6195254629629628E-3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A63" s="5" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
+      <c r="B63" s="9">
+        <v>7.6959490740740732E-4</v>
+      </c>
+      <c r="C63" s="9">
+        <v>7.8141203703703695E-4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
+      <c r="B64" s="9">
+        <v>9.7805555555555558E-4</v>
+      </c>
+      <c r="C64" s="9">
+        <v>9.9010416666666669E-4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
+      <c r="B65" s="9">
+        <v>1.168113425925926E-3</v>
+      </c>
+      <c r="C65" s="9">
+        <v>1.1832407407407408E-3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
+      <c r="B66" s="9">
+        <v>1.3700462962962963E-3</v>
+      </c>
+      <c r="C66" s="9">
+        <v>1.3820023148148149E-3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="67" spans="1:1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A67" s="5" t="s">
+      <c r="B67" s="9">
+        <v>1.5531828703703704E-3</v>
+      </c>
+      <c r="C67" s="9">
+        <v>1.5624537037037037E-3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A68" s="5" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
+      <c r="B68" s="9">
+        <v>7.9972222222222228E-4</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
+      <c r="B69" s="9">
+        <v>9.9252314814814819E-4</v>
+      </c>
+      <c r="C69" s="9">
+        <v>1.004675925925926E-3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
+      <c r="B70" s="9">
+        <v>1.1833564814814814E-3</v>
+      </c>
+      <c r="C70" s="9">
+        <v>1.1974537037037038E-3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
+      <c r="B71" s="9">
+        <v>1.3842592592592591E-3</v>
+      </c>
+      <c r="C71" s="9">
+        <v>6.9444444444444447E-4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="72" spans="1:1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A72" s="5" t="s">
+    <row r="73" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A73" s="5" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
+      <c r="B74" s="9">
+        <v>1.0086689814814815E-3</v>
+      </c>
+      <c r="C74" s="9">
+        <v>1.0221643518518518E-3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
+      <c r="B75" s="9">
+        <v>1.2005439814814815E-3</v>
+      </c>
+      <c r="C75" s="9">
+        <v>1.2178240740740741E-3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
+      <c r="B76" s="9">
+        <v>1.3870138888888888E-3</v>
+      </c>
+      <c r="C76" s="9">
+        <v>1.3977546296296297E-3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="77" spans="1:1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A77" s="5" t="s">
+      <c r="B77" s="9">
+        <v>1.5806018518518517E-3</v>
+      </c>
+      <c r="C77" s="9">
+        <v>1.5926273148148149E-3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A78" s="5" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
+      <c r="B78" s="9">
+        <v>8.353124999999999E-4</v>
+      </c>
+      <c r="C78" s="9">
+        <v>8.5023148148148154E-4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
+      <c r="B79" s="9">
+        <v>1.0238657407407408E-3</v>
+      </c>
+      <c r="C79" s="9">
+        <v>1.0372222222222221E-3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A80" t="s">
+      <c r="B80" s="9">
+        <v>1.5935069444444445E-3</v>
+      </c>
+      <c r="C80" s="9">
+        <v>1.6048379629629631E-3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="81" spans="1:1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A81" s="5" t="s">
+      <c r="B81" s="9">
+        <v>1.4014930555555556E-3</v>
+      </c>
+      <c r="C81" s="9">
+        <v>1.4147337962962963E-3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>200</v>
+      </c>
+      <c r="B82" s="9">
+        <v>1.1408333333333333E-3</v>
+      </c>
+      <c r="C82" s="9">
+        <v>1.1534837962962963E-3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A83" s="5" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A82" t="s">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A83" t="s">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A84" t="s">
+      <c r="B85" s="9">
+        <v>1.0393055555555555E-3</v>
+      </c>
+      <c r="C85" s="9">
+        <v>1.0559953703703703E-3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A85" t="s">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="86" spans="1:1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A86" s="5" t="s">
+      <c r="B87" s="9">
+        <v>1.4176041666666666E-3</v>
+      </c>
+      <c r="C87" s="9">
+        <v>1.4307060185185184E-3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A88" s="5" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A87" t="s">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A88" t="s">
+      <c r="B89" s="9">
+        <v>8.6579861111111124E-4</v>
+      </c>
+      <c r="C89" s="9">
+        <v>8.7839120370370371E-4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A89" t="s">
+      <c r="B90" s="9">
+        <v>1.05875E-3</v>
+      </c>
+      <c r="C90" s="9">
+        <v>1.0693518518518517E-3</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A90" t="s">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="91" spans="1:1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A91" s="5" t="s">
+      <c r="B92" s="9">
+        <v>1.432650462962963E-3</v>
+      </c>
+      <c r="C92" s="9">
+        <v>1.4435763888888888E-3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A93" s="5" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A92" t="s">
+      <c r="B93" s="9">
+        <v>1.6210185185185186E-3</v>
+      </c>
+      <c r="C93" s="9">
+        <v>1.6399768518518517E-3</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A93" t="s">
+      <c r="B94" s="9">
+        <v>8.8039351851851853E-4</v>
+      </c>
+      <c r="C94" s="9">
+        <v>8.9284722222222218E-4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A94" t="s">
+      <c r="B95" s="9">
+        <v>1.0716898148148148E-3</v>
+      </c>
+      <c r="C95" s="9">
+        <v>1.0821296296296297E-3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A95" t="s">
+      <c r="B96" s="9">
+        <v>1.2623726851851852E-3</v>
+      </c>
+      <c r="C96" s="9">
+        <v>1.272337962962963E-3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="96" spans="1:1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A96" s="5" t="s">
+      <c r="B97" s="9">
+        <v>1.4450462962962963E-3</v>
+      </c>
+      <c r="C97" s="9">
+        <v>1.4576736111111112E-3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>201</v>
+      </c>
+      <c r="B98" s="9">
+        <v>1.1553819444444446E-3</v>
+      </c>
+      <c r="C98" s="9">
+        <v>1.1669560185185186E-3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+      <c r="A99" s="5" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A97" t="s">
+      <c r="B99" s="9">
+        <v>1.6435763888888889E-3</v>
+      </c>
+      <c r="C99" s="9">
+        <v>1.6551388888888887E-3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A98" t="s">
+      <c r="B100" s="9">
+        <v>8.9537037037037037E-4</v>
+      </c>
+      <c r="C100" s="9">
+        <v>9.0715277777777777E-4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A99" t="s">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A100" t="s">
+      <c r="B102" s="9">
+        <v>1.2723842592592591E-3</v>
+      </c>
+      <c r="C102" s="9">
+        <v>1.2889930555555556E-3</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="101" spans="1:1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A101" s="5" t="s">
+      <c r="B103" s="9">
+        <v>1.4612731481481482E-3</v>
+      </c>
+      <c r="C103" s="9">
+        <v>1.469537037037037E-3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+      <c r="A104" s="5" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A102" t="s">
+    <row r="105" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+      <c r="A105" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="B105" s="9">
+        <v>1.6924189814814814E-3</v>
+      </c>
+      <c r="C105" s="9">
+        <v>1.7041898148148146E-3</v>
+      </c>
+      <c r="G105" s="18">
+        <v>0.11041666666666666</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+      <c r="A106" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B106" s="9">
+        <v>1.5638541666666665E-3</v>
+      </c>
+      <c r="C106" s="9">
+        <v>1.578564814814815E-3</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="A107" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="B107" s="9">
+        <v>1.5056597222222223E-3</v>
+      </c>
+      <c r="C107" s="9">
+        <v>1.5171064814814815E-3</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A108" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="B108" s="9">
+        <v>1.3440509259259261E-3</v>
+      </c>
+      <c r="C108" s="9">
+        <v>1.3535995370370371E-3</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A103" t="s">
+      <c r="B109" s="9">
+        <v>9.0853009259259261E-4</v>
+      </c>
+      <c r="C109" s="9">
+        <v>9.2133101851851859E-4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A104" t="s">
+      <c r="B110" s="9">
+        <v>1.0987500000000001E-3</v>
+      </c>
+      <c r="C110" s="9">
+        <v>1.1127430555555554E-3</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A111" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="B111" s="9">
+        <v>1.3271759259259261E-3</v>
+      </c>
+      <c r="C111" s="9">
+        <v>1.3425925925925925E-3</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A105" t="s">
+      <c r="B112" s="9">
+        <v>1.2961574074074073E-3</v>
+      </c>
+      <c r="C112" s="9">
+        <v>1.3107060185185186E-3</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="108" spans="1:1" ht="23" x14ac:dyDescent="0.25">
-      <c r="A108" s="6" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1" ht="23" x14ac:dyDescent="0.2">
-      <c r="A109" s="7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1" ht="23" x14ac:dyDescent="0.25">
-      <c r="A110" s="6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1" ht="23" x14ac:dyDescent="0.25">
-      <c r="A111" s="6" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1" ht="23" x14ac:dyDescent="0.2">
-      <c r="A112" s="7" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1" ht="28" x14ac:dyDescent="0.2">
-      <c r="A116" s="8" t="s">
+      <c r="B113" s="9">
+        <v>1.4719675925925926E-3</v>
+      </c>
+      <c r="C113" s="9">
+        <v>1.4855787037037036E-3</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>194</v>
+      </c>
+      <c r="B114" s="9">
+        <v>8.5195601851851849E-4</v>
+      </c>
+      <c r="C114" s="9">
+        <v>8.6290509259259263E-4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>196</v>
+      </c>
+      <c r="B115" s="9">
+        <v>8.9548611111111111E-4</v>
+      </c>
+      <c r="C115" s="9">
+        <v>9.0753472222222223E-4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" ht="26" x14ac:dyDescent="0.35">
+      <c r="A116" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="B116" s="9">
+        <v>9.375347222222222E-4</v>
+      </c>
+      <c r="C116" s="9">
+        <v>9.499189814814816E-4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" ht="26" x14ac:dyDescent="0.35">
+      <c r="A117" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="B117" s="9">
+        <v>9.501041666666667E-4</v>
+      </c>
+      <c r="C117" s="9">
+        <v>9.6184027777777793E-4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" ht="26" x14ac:dyDescent="0.35">
+      <c r="A118" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="B118" s="9">
+        <v>1.1285995370370369E-3</v>
+      </c>
+      <c r="C118" s="9">
+        <v>1.138425925925926E-3</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" ht="26" x14ac:dyDescent="0.35">
+      <c r="A119" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="B119" s="9">
+        <v>1.4885300925925927E-3</v>
+      </c>
+      <c r="C119" s="9">
+        <v>1.5030208333333332E-3</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" ht="26" x14ac:dyDescent="0.35">
+      <c r="A120" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="B120" s="9">
+        <v>9.2317129629629628E-4</v>
+      </c>
+      <c r="C120" s="9">
+        <v>9.3604166666666662E-4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" ht="23" x14ac:dyDescent="0.25">
+      <c r="A121" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B121" s="9">
+        <v>1.8364583333333336E-3</v>
+      </c>
+      <c r="C121" s="9">
+        <v>1.9106365740740741E-3</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" ht="23" x14ac:dyDescent="0.2">
+      <c r="A122" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="B122" s="9">
+        <v>1.969861111111111E-3</v>
+      </c>
+      <c r="C122" s="9">
+        <v>2.0916550925925924E-3</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" ht="23" x14ac:dyDescent="0.25">
+      <c r="A123" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="B123" s="9">
+        <v>2.0916550925925924E-3</v>
+      </c>
+      <c r="C123" s="9">
+        <v>2.2372453703703703E-3</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" ht="23" x14ac:dyDescent="0.25">
+      <c r="A124" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="B124" s="9">
+        <v>2.2445833333333332E-3</v>
+      </c>
+      <c r="C124" s="9">
+        <v>2.3876041666666663E-3</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" ht="23" x14ac:dyDescent="0.2">
+      <c r="A125" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="B125" s="9">
+        <v>2.3967824074074074E-3</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" ht="28" x14ac:dyDescent="0.2">
+      <c r="A129" s="8" t="s">
         <v>107</v>
+      </c>
+      <c r="B129" s="9">
+        <v>2.5313541666666666E-3</v>
+      </c>
+      <c r="C129" s="9">
+        <v>3.3039120370370366E-3</v>
       </c>
     </row>
   </sheetData>

--- a/cropvideo/marathi.xlsx
+++ b/cropvideo/marathi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dhaneshkumarkapadia/Desktop/swinTransformer/cropvideo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EA2B0A7-8C44-B843-BE8C-68CBC0420B53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{474C59AB-BFF6-B844-977D-97635314941F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="140" yWindow="600" windowWidth="26740" windowHeight="15200" activeTab="2" xr2:uid="{F583F2BC-D1B1-3A48-88E7-21C7FADE06E4}"/>
   </bookViews>
@@ -4435,9 +4435,7 @@
       <c r="C105" s="9">
         <v>1.7041898148148146E-3</v>
       </c>
-      <c r="G105" s="18">
-        <v>0.11041666666666666</v>
-      </c>
+      <c r="G105" s="18"/>
     </row>
     <row r="106" spans="1:7" ht="30" x14ac:dyDescent="0.2">
       <c r="A106" s="5" t="s">
@@ -4654,6 +4652,9 @@
       </c>
       <c r="B125" s="9">
         <v>2.3967824074074074E-3</v>
+      </c>
+      <c r="C125" s="9">
+        <v>2.4992245370370368E-3</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="28" x14ac:dyDescent="0.2">
